--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB VALLS TALLERS PABLO MARTÍNEZ.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB VALLS TALLERS PABLO MARTÍNEZ.xlsx
@@ -565,13 +565,13 @@
         <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>26.2574</v>
+        <v>24.6254</v>
       </c>
       <c r="E2" t="n">
-        <v>14.1266</v>
+        <v>15.2091</v>
       </c>
       <c r="F2" t="n">
-        <v>12.1307</v>
+        <v>9.416399999999999</v>
       </c>
       <c r="G2" t="n">
         <v>4.870800000000001</v>
@@ -610,13 +610,13 @@
         <v>42.6527</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3081</v>
+        <v>2.6764</v>
       </c>
       <c r="T2" t="n">
-        <v>-5.8584</v>
+        <v>-4.776199999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>10.167</v>
+        <v>7.4528</v>
       </c>
       <c r="V2" t="n">
         <v>30.9651</v>
@@ -643,13 +643,13 @@
         <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>17.9739</v>
+        <v>13.7483</v>
       </c>
       <c r="E3" t="n">
-        <v>7.303400000000001</v>
+        <v>2.7118</v>
       </c>
       <c r="F3" t="n">
-        <v>10.6706</v>
+        <v>11.0363</v>
       </c>
       <c r="G3" t="n">
         <v>2.5454</v>
@@ -688,13 +688,13 @@
         <v>32.932</v>
       </c>
       <c r="S3" t="n">
-        <v>7.2154</v>
+        <v>2.9898</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5212</v>
+        <v>-3.0702</v>
       </c>
       <c r="U3" t="n">
-        <v>5.694</v>
+        <v>6.0599</v>
       </c>
       <c r="V3" t="n">
         <v>3.0553</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ACOSTA ALMONTE</t>
+          <t>G. FABREGAS CANALS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>17.1775</v>
+        <v>12.6629</v>
       </c>
       <c r="E4" t="n">
-        <v>10.189</v>
+        <v>-5.852200000000002</v>
       </c>
       <c r="F4" t="n">
-        <v>6.9884</v>
+        <v>18.5154</v>
       </c>
       <c r="G4" t="n">
-        <v>4.732099999999999</v>
+        <v>19.9333</v>
       </c>
       <c r="H4" t="n">
-        <v>5.0024</v>
+        <v>13.7152</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2701999999999998</v>
+        <v>6.218</v>
       </c>
       <c r="J4" t="n">
-        <v>9.486800000000001</v>
+        <v>32.5446</v>
       </c>
       <c r="K4" t="n">
-        <v>7.1147</v>
+        <v>22.7271</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3722</v>
+        <v>9.817500000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.7547</v>
+        <v>-12.6113</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.1124</v>
+        <v>-9.0121</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.6424</v>
+        <v>-3.5998</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9919000000000002</v>
+        <v>-11.3078</v>
       </c>
       <c r="Q4" t="n">
-        <v>-13.2917</v>
+        <v>-45.6281</v>
       </c>
       <c r="R4" t="n">
-        <v>12.2999</v>
+        <v>34.3205</v>
       </c>
       <c r="S4" t="n">
-        <v>18.6966</v>
+        <v>1.7313</v>
       </c>
       <c r="T4" t="n">
-        <v>12.7545</v>
+        <v>-6.5335</v>
       </c>
       <c r="U4" t="n">
-        <v>5.9418</v>
+        <v>8.264699999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-5.2591</v>
+        <v>2.3066</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2394</v>
+        <v>13.7647</v>
       </c>
       <c r="X4" t="n">
-        <v>-6.4986</v>
+        <v>-11.4582</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.8174</v>
+        <v>7.1112</v>
       </c>
       <c r="E5" t="n">
-        <v>5.8846</v>
+        <v>6.0943</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9328</v>
+        <v>1.017</v>
       </c>
       <c r="G5" t="n">
         <v>7.5115</v>
@@ -844,13 +844,13 @@
         <v>3.1741</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0459</v>
+        <v>0.248</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2382</v>
+        <v>0.4479</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2841</v>
+        <v>-0.1999</v>
       </c>
       <c r="V5" t="n">
         <v>0.1453</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. NGOMO MIFUMU</t>
+          <t>A. ROSA BEJARANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>6.6707</v>
+        <v>6.8094</v>
       </c>
       <c r="E6" t="n">
-        <v>-11.6139</v>
+        <v>3.457399999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>18.285</v>
+        <v>3.3517</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.055</v>
+        <v>-4.7631</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9861</v>
+        <v>9.870700000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-5.040699999999999</v>
+        <v>-14.6338</v>
       </c>
       <c r="J6" t="n">
-        <v>14.1543</v>
+        <v>21.6615</v>
       </c>
       <c r="K6" t="n">
-        <v>13.9312</v>
+        <v>27.5914</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2231000000000004</v>
+        <v>-5.9299</v>
       </c>
       <c r="M6" t="n">
-        <v>-16.2088</v>
+        <v>-26.4245</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.9448</v>
+        <v>-17.7204</v>
       </c>
       <c r="O6" t="n">
-        <v>-5.2641</v>
+        <v>-8.7041</v>
       </c>
       <c r="P6" t="n">
-        <v>-7.538399999999999</v>
+        <v>6.5468</v>
       </c>
       <c r="Q6" t="n">
-        <v>-50.3894</v>
+        <v>-31.3444</v>
       </c>
       <c r="R6" t="n">
-        <v>42.8512</v>
+        <v>37.8912</v>
       </c>
       <c r="S6" t="n">
-        <v>17.8265</v>
+        <v>1.414399999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>8.709200000000001</v>
+        <v>-3.9202</v>
       </c>
       <c r="U6" t="n">
-        <v>9.1175</v>
+        <v>5.3343</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.562600000000001</v>
+        <v>3.611499999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>15.9117</v>
+        <v>17.0611</v>
       </c>
       <c r="X6" t="n">
-        <v>-17.4741</v>
+        <v>-13.4494</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ROSA BEJARANO</t>
+          <t>D. ACOSTA ALMONTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>6.489000000000002</v>
+        <v>6.707000000000002</v>
       </c>
       <c r="E7" t="n">
-        <v>5.050500000000001</v>
+        <v>1.5674</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4387</v>
+        <v>5.1395</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.7631</v>
+        <v>4.732099999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>9.870700000000001</v>
+        <v>5.0024</v>
       </c>
       <c r="I7" t="n">
-        <v>-14.6338</v>
+        <v>-0.2701999999999998</v>
       </c>
       <c r="J7" t="n">
-        <v>21.6615</v>
+        <v>9.486800000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>27.5914</v>
+        <v>7.1147</v>
       </c>
       <c r="L7" t="n">
-        <v>-5.9299</v>
+        <v>2.3722</v>
       </c>
       <c r="M7" t="n">
-        <v>-26.4245</v>
+        <v>-4.7547</v>
       </c>
       <c r="N7" t="n">
-        <v>-17.7204</v>
+        <v>-2.1124</v>
       </c>
       <c r="O7" t="n">
-        <v>-8.7041</v>
+        <v>-2.6424</v>
       </c>
       <c r="P7" t="n">
-        <v>6.5468</v>
+        <v>-0.9919000000000002</v>
       </c>
       <c r="Q7" t="n">
-        <v>-31.3444</v>
+        <v>-13.2917</v>
       </c>
       <c r="R7" t="n">
-        <v>37.8912</v>
+        <v>12.2999</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0941</v>
+        <v>8.225899999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.3275</v>
+        <v>4.133</v>
       </c>
       <c r="U7" t="n">
-        <v>3.4215</v>
+        <v>4.0928</v>
       </c>
       <c r="V7" t="n">
-        <v>3.611499999999999</v>
+        <v>-5.2591</v>
       </c>
       <c r="W7" t="n">
-        <v>17.0611</v>
+        <v>1.2394</v>
       </c>
       <c r="X7" t="n">
-        <v>-13.4494</v>
+        <v>-6.4986</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. FABREGAS CANALS</t>
+          <t>G. GUTIÉRREZ MONREAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>6.363900000000001</v>
+        <v>6.6027</v>
       </c>
       <c r="E8" t="n">
-        <v>-11.6736</v>
+        <v>-0.9990999999999994</v>
       </c>
       <c r="F8" t="n">
-        <v>18.0373</v>
+        <v>7.6018</v>
       </c>
       <c r="G8" t="n">
-        <v>19.9333</v>
+        <v>15.3931</v>
       </c>
       <c r="H8" t="n">
-        <v>13.7152</v>
+        <v>7.7628</v>
       </c>
       <c r="I8" t="n">
-        <v>6.218</v>
+        <v>7.629999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>32.5446</v>
+        <v>29.1848</v>
       </c>
       <c r="K8" t="n">
-        <v>22.7271</v>
+        <v>15.7979</v>
       </c>
       <c r="L8" t="n">
-        <v>9.817500000000001</v>
+        <v>13.3867</v>
       </c>
       <c r="M8" t="n">
-        <v>-12.6113</v>
+        <v>-13.792</v>
       </c>
       <c r="N8" t="n">
-        <v>-9.0121</v>
+        <v>-8.0351</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.5998</v>
+        <v>-5.757</v>
       </c>
       <c r="P8" t="n">
-        <v>-11.3078</v>
+        <v>1.785300000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-45.6281</v>
+        <v>-39.2798</v>
       </c>
       <c r="R8" t="n">
-        <v>34.3205</v>
+        <v>41.0654</v>
       </c>
       <c r="S8" t="n">
-        <v>-4.5679</v>
+        <v>-7.0115</v>
       </c>
       <c r="T8" t="n">
-        <v>-12.3547</v>
+        <v>-8.981999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>7.7865</v>
+        <v>1.9702</v>
       </c>
       <c r="V8" t="n">
-        <v>2.3066</v>
+        <v>-3.564</v>
       </c>
       <c r="W8" t="n">
-        <v>13.7647</v>
+        <v>18.0782</v>
       </c>
       <c r="X8" t="n">
-        <v>-11.4582</v>
+        <v>-21.6419</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. OLLE GATELL</t>
+          <t>J. CAÑELLAS VAQUÉ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8869</v>
+        <v>0.8423999999999994</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1327</v>
+        <v>0.4338000000000002</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2458</v>
+        <v>0.4081999999999996</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9265</v>
+        <v>-1.9921</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02989999999999998</v>
+        <v>0.4302</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8966000000000001</v>
+        <v>-2.4224</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1005</v>
+        <v>2.009</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0202</v>
+        <v>1.4719</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0803</v>
+        <v>0.5374999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8260000000000001</v>
+        <v>-4.0015</v>
       </c>
       <c r="N9" t="n">
-        <v>0.009800000000000031</v>
+        <v>-1.0414</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8163</v>
+        <v>-2.96</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1903</v>
+        <v>9.7209</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7936</v>
+        <v>9.7209</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3571</v>
+        <v>-0.9255</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2494</v>
+        <v>-1.5754</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1078</v>
+        <v>0.6498999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.266</v>
+        <v>-5.9611</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.266</v>
+        <v>-5.9611</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. CAÑELLAS VAQUÉ</t>
+          <t>I. OLLE GATELL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.574</v>
+        <v>-0.7847999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0172</v>
+        <v>-2.0307</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5566999999999998</v>
+        <v>1.2458</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9921</v>
+        <v>0.9265</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4302</v>
+        <v>0.02989999999999998</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4224</v>
+        <v>0.8966000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>2.009</v>
+        <v>0.1005</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4719</v>
+        <v>0.0202</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5374999999999999</v>
+        <v>0.0803</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.0015</v>
+        <v>0.8260000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0414</v>
+        <v>0.009800000000000031</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.96</v>
+        <v>0.8163</v>
       </c>
       <c r="P10" t="n">
-        <v>9.7209</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R10" t="n">
-        <v>9.7209</v>
+        <v>0.7936</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.3413</v>
+        <v>-0.2551</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.0263</v>
+        <v>-0.1474</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3149</v>
+        <v>-0.1078</v>
       </c>
       <c r="V10" t="n">
-        <v>-5.9611</v>
+        <v>-0.266</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.9611</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>23</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2107</v>
+        <v>-2.5722</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.0746</v>
+        <v>-8.9899</v>
       </c>
       <c r="F11" t="n">
-        <v>5.864100000000001</v>
+        <v>6.417700000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1694</v>
@@ -1312,13 +1312,13 @@
         <v>34.7174</v>
       </c>
       <c r="S11" t="n">
-        <v>1.729</v>
+        <v>2.367599999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3355</v>
+        <v>-1.2508</v>
       </c>
       <c r="U11" t="n">
-        <v>3.0649</v>
+        <v>3.6183</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7863000000000002</v>
@@ -1345,13 +1345,13 @@
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.335699999999999</v>
+        <v>-7.2891</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.898400000000001</v>
+        <v>-5.5923</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4375</v>
+        <v>-1.6969</v>
       </c>
       <c r="G12" t="n">
         <v>-4.622999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>5.1581</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2611</v>
+        <v>-1.2145</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2354</v>
+        <v>-0.9294</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0256</v>
+        <v>-0.2851</v>
       </c>
       <c r="V12" t="n">
         <v>0.5319</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
+          <t>O. NGOMO MIFUMU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.924199999999999</v>
+        <v>-7.7086</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.154</v>
+        <v>-23.427</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.77</v>
+        <v>15.7186</v>
       </c>
       <c r="G13" t="n">
-        <v>-12.2175</v>
+        <v>-2.055</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.2989</v>
+        <v>2.9861</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.9186</v>
+        <v>-5.040699999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.0118</v>
+        <v>14.1543</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.2167</v>
+        <v>13.9312</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2048</v>
+        <v>0.2231000000000004</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.2056</v>
+        <v>-16.2088</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.0821</v>
+        <v>-10.9448</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.1235</v>
+        <v>-5.2641</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3967999999999999</v>
+        <v>-7.538399999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.5466</v>
+        <v>-50.3894</v>
       </c>
       <c r="R13" t="n">
-        <v>6.9435</v>
+        <v>42.8512</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2504999999999998</v>
+        <v>3.4472</v>
       </c>
       <c r="T13" t="n">
-        <v>0.06269999999999998</v>
+        <v>-3.1035</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3134</v>
+        <v>6.551</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1469</v>
+        <v>-1.562600000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>2.3416</v>
+        <v>15.9117</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1947</v>
+        <v>-17.4741</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. GUTIÉRREZ MONREAL</t>
+          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.437</v>
+        <v>-10.4843</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.6523</v>
+        <v>-9.01</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2155999999999998</v>
+        <v>-1.4742</v>
       </c>
       <c r="G14" t="n">
-        <v>15.3931</v>
+        <v>-12.2175</v>
       </c>
       <c r="H14" t="n">
-        <v>7.7628</v>
+        <v>-8.2989</v>
       </c>
       <c r="I14" t="n">
-        <v>7.629999999999999</v>
+        <v>-3.9186</v>
       </c>
       <c r="J14" t="n">
-        <v>29.1848</v>
+        <v>-4.0118</v>
       </c>
       <c r="K14" t="n">
-        <v>15.7979</v>
+        <v>-5.2167</v>
       </c>
       <c r="L14" t="n">
-        <v>13.3867</v>
+        <v>1.2048</v>
       </c>
       <c r="M14" t="n">
-        <v>-13.792</v>
+        <v>-8.2056</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.0351</v>
+        <v>-3.0821</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.757</v>
+        <v>-5.1235</v>
       </c>
       <c r="P14" t="n">
-        <v>1.785300000000001</v>
+        <v>0.3967999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-39.2798</v>
+        <v>-6.5466</v>
       </c>
       <c r="R14" t="n">
-        <v>41.0654</v>
+        <v>6.9435</v>
       </c>
       <c r="S14" t="n">
-        <v>-24.0509</v>
+        <v>-0.8105</v>
       </c>
       <c r="T14" t="n">
-        <v>-18.6348</v>
+        <v>-0.7931999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.4163</v>
+        <v>-0.01739999999999997</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.564</v>
+        <v>2.1469</v>
       </c>
       <c r="W14" t="n">
-        <v>18.0782</v>
+        <v>2.3416</v>
       </c>
       <c r="X14" t="n">
-        <v>-21.6419</v>
+        <v>-0.1947</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>-24.7068</v>
+        <v>-13.2589</v>
       </c>
       <c r="E15" t="n">
-        <v>-23.4591</v>
+        <v>-16.5894</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2478</v>
+        <v>3.3305</v>
       </c>
       <c r="G15" t="n">
         <v>3.1734</v>
@@ -1624,13 +1624,13 @@
         <v>31.7415</v>
       </c>
       <c r="S15" t="n">
-        <v>-17.5228</v>
+        <v>-6.0746</v>
       </c>
       <c r="T15" t="n">
-        <v>-14.0099</v>
+        <v>-7.1401</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.5129</v>
+        <v>1.0654</v>
       </c>
       <c r="V15" t="n">
         <v>-2.8188</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-54.6567</v>
+        <v>-28.9664</v>
       </c>
       <c r="E16" t="n">
-        <v>-43.0404</v>
+        <v>-29.6125</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.6163</v>
+        <v>0.6456999999999997</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5260000000000016</v>
@@ -1702,13 +1702,13 @@
         <v>52.5716</v>
       </c>
       <c r="S16" t="n">
-        <v>-35.741</v>
+        <v>-10.0508</v>
       </c>
       <c r="T16" t="n">
-        <v>-24.3986</v>
+        <v>-10.9707</v>
       </c>
       <c r="U16" t="n">
-        <v>-11.3428</v>
+        <v>0.9197999999999997</v>
       </c>
       <c r="V16" t="n">
         <v>-3.312500000000001</v>
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-25.98219999999999</v>
+        <v>8.045000000000012</v>
       </c>
       <c r="E17" t="n">
-        <v>-84.16210000000001</v>
+        <v>-72.6293</v>
       </c>
       <c r="F17" t="n">
-        <v>58.1807</v>
+        <v>80.6735</v>
       </c>
       <c r="G17" t="n">
         <v>30.73999999999999</v>
@@ -1777,19 +1777,19 @@
         <v>-427.5149000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>388.8336</v>
+        <v>388.8335999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>-37.2688</v>
+        <v>-3.241900000000003</v>
       </c>
       <c r="T17" t="n">
-        <v>-60.1447</v>
+        <v>-48.61170000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>22.8754</v>
+        <v>45.3689</v>
       </c>
       <c r="V17" t="n">
-        <v>19.2322</v>
+        <v>19.23220000000001</v>
       </c>
       <c r="W17" t="n">
         <v>164.6706</v>
